--- a/artfynd/A 27870-2022 artfynd.xlsx
+++ b/artfynd/A 27870-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128184370</v>
       </c>
       <c r="B2" t="n">
-        <v>56559</v>
+        <v>56571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128184371</v>
       </c>
       <c r="B3" t="n">
-        <v>56554</v>
+        <v>56566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128184372</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
+        <v>56552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27870-2022 artfynd.xlsx
+++ b/artfynd/A 27870-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128184370</v>
       </c>
       <c r="B2" t="n">
-        <v>56571</v>
+        <v>56575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128184371</v>
       </c>
       <c r="B3" t="n">
-        <v>56566</v>
+        <v>56570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128184372</v>
       </c>
       <c r="B4" t="n">
-        <v>56552</v>
+        <v>56556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27870-2022 artfynd.xlsx
+++ b/artfynd/A 27870-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128184370</v>
       </c>
       <c r="B2" t="n">
-        <v>56575</v>
+        <v>56602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>128184371</v>
       </c>
       <c r="B3" t="n">
-        <v>56570</v>
+        <v>56597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128184372</v>
       </c>
       <c r="B4" t="n">
-        <v>56556</v>
+        <v>56583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27870-2022 artfynd.xlsx
+++ b/artfynd/A 27870-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128184370</v>
+        <v>128184371</v>
       </c>
       <c r="B2" t="n">
-        <v>56602</v>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128184371</v>
+        <v>128184370</v>
       </c>
       <c r="B3" t="n">
-        <v>56597</v>
+        <v>56835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -900,7 +900,7 @@
         <v>128184372</v>
       </c>
       <c r="B4" t="n">
-        <v>56583</v>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,6 +1005,108 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131136726</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>C, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>692839</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6665409</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inventering Sweco.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Ringbom</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27870-2022 artfynd.xlsx
+++ b/artfynd/A 27870-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128184371</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128184370</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128184372</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,8 +1127,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131136726</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>